--- a/data/dividends_info_20261028.xlsx
+++ b/data/dividends_info_20261028.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.70999908447266</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.205902543777383</v>
+        <v>0.2075167217351112</v>
       </c>
       <c r="J2" t="n">
         <v>138</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>60.29999923706055</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.160862369579895</v>
+        <v>1.153212506098331</v>
       </c>
       <c r="J3" t="n">
         <v>117</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.699999809265137</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6896551875334813</v>
+        <v>0.6864988738131719</v>
       </c>
       <c r="J4" t="n">
         <v>47</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.70999908447266</v>
+        <v>43.36999893188477</v>
       </c>
       <c r="I6" t="n">
-        <v>0.205902543777383</v>
+        <v>0.2075167217351112</v>
       </c>
       <c r="J6" t="n">
         <v>47</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26.52000045776367</v>
+        <v>26.88999938964844</v>
       </c>
       <c r="I7" t="n">
-        <v>1.734539939894066</v>
+        <v>1.710673151510303</v>
       </c>
       <c r="J7" t="n">
         <v>40</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.945999979972839</v>
+        <v>1.944000005722046</v>
       </c>
       <c r="I8" t="n">
-        <v>3.956834573095664</v>
+        <v>3.960905338135554</v>
       </c>
       <c r="J8" t="n">
         <v>26</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>52.65000152587891</v>
+        <v>52.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5887939050630921</v>
+        <v>0.5904761904761905</v>
       </c>
       <c r="J9" t="n">
         <v>26</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.52000045776367</v>
+        <v>26.88999938964844</v>
       </c>
       <c r="I10" t="n">
-        <v>1.018099529937821</v>
+        <v>1.004090762843004</v>
       </c>
       <c r="J10" t="n">
         <v>26</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>26.92000007629395</v>
+        <v>27.19000053405762</v>
       </c>
       <c r="I11" t="n">
-        <v>2.19167904282274</v>
+        <v>2.169915367456424</v>
       </c>
       <c r="J11" t="n">
         <v>26</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10.23999977111816</v>
+        <v>10.18000030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>2.050781295838534</v>
+        <v>2.062868307511056</v>
       </c>
       <c r="J12" t="n">
         <v>19</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.010000228881836</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>3.327786894896843</v>
+        <v>3.355704676508394</v>
       </c>
       <c r="J13" t="n">
         <v>19</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.75</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I14" t="n">
-        <v>1.217391304347826</v>
+        <v>1.228070216532597</v>
       </c>
       <c r="J14" t="n">
         <v>12</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8.100000381469727</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7407407058555365</v>
+        <v>0.7317073340929389</v>
       </c>
       <c r="J15" t="n">
         <v>12</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.885000228881836</v>
+        <v>9.710000038146973</v>
       </c>
       <c r="I16" t="n">
-        <v>4.653515319665642</v>
+        <v>4.737384121450375</v>
       </c>
       <c r="J16" t="n">
         <v>-2</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7.71999979019165</v>
+        <v>7.78000020980835</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4922279926520133</v>
+        <v>0.4884318634348222</v>
       </c>
       <c r="J20" t="n">
         <v>-30</v>
@@ -1392,7 +1392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C197"/>
+  <dimension ref="A1:C237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1663,14 +1663,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1697,14 +1697,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1969,14 +1969,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2037,14 +2037,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2190,14 +2190,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2411,14 +2411,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2479,14 +2479,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2503,7 +2503,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2530,14 +2530,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2554,7 +2554,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2588,7 +2588,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2649,14 +2649,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2860,7 +2860,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2921,14 +2921,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3159,14 +3159,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3217,7 +3217,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3244,14 +3244,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3278,14 +3278,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3295,14 +3295,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3319,29 +3319,29 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3370,12 +3370,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3387,12 +3387,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3404,29 +3404,29 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3438,12 +3438,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3455,12 +3455,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3472,12 +3472,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3533,14 +3533,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3642,7 +3642,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3693,7 +3693,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3720,14 +3720,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3771,14 +3771,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3795,12 +3795,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3812,29 +3812,29 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3846,29 +3846,29 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3880,41 +3880,41 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4033,7 +4033,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4050,7 +4050,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4135,7 +4135,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4169,7 +4169,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4179,14 +4179,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4220,7 +4220,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4305,29 +4305,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4339,46 +4339,46 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4390,12 +4390,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4407,29 +4407,29 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4441,12 +4441,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4458,12 +4458,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4475,29 +4475,29 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4509,12 +4509,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4526,12 +4526,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4543,12 +4543,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4560,80 +4560,80 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4645,12 +4645,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4662,46 +4662,46 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4713,34 +4713,714 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>IRCE s.p.a</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>INTERPUMP GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>EUROTECH S.p.A.</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ERG S.p.A.</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ACEA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>MARR S.p.A.</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>MARR S.p.A.</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Unipol S.p.A.</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ERG S.p.A.</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>EMAK S.p.A.</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>EL.EN. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CY4Gate S.p.A.</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLASS EDITORI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLABO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ECOSUNTEK S.p.A.</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>EuroGroup Laminations S.p.A.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>GREEN OLEO S.p.A</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>OMER S.p.A.</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-11-16</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CIRCLE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-11-17</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Gens Aurea S.p.A.</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>eVISO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Gens Aurea S.p.A.</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CIRCLE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SAIPEM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>PIQUADRO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>UNIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>DHH S.p.A.</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>S.S. Lazio S.p.A.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
           <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>2026-11-24</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Lindbergh S.p.A.</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>OPS Retail S.p.A.</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4768,61 +5448,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Bper Banca S.P.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>